--- a/basedatos_partidas/salida/descompuestos/CT-02-01-100.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-01-100.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 02 Demoliciones y desmontajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-02-01-100.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-01-100.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantado de piso existente de parquet o de tablilla de madera, incluidos los rastreles o el adhesivo de fijación al contrapiso, ejecutado con medios manuales mediante palanca y espátula. Incluye el retiro previo de las molduras de remate, el rascado de los restos de adhesivo adheridos al contrapiso, la extracción de los clavos o tornillos que queden en la base, el retiro del material en sacos hasta el punto de acopio y la limpieza de la superficie resultante. No incluye el bote del escombro. Medido en superficie realmente levantada.
+          <t xml:space="preserve">Levantado de piso existente de parquet o de tablilla de madera, incluidos los rastreles o el adhesivo de fijación al afirmado, ejecutado con medios manuales mediante palanca y espátula. Incluye el retiro previo de las molduras de remate, el rascado de los restos de adhesivo adheridos al afirmado, la extracción de los clavos o tornillos que queden en la base, el retiro del material en sacos hasta el punto de acopio y la limpieza de la superficie resultante. No incluye el bote del escombro. Medido en superficie realmente levantada.
 </t>
         </is>
       </c>
